--- a/base_execucao/empenhos.xlsx
+++ b/base_execucao/empenhos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB8"/>
+  <dimension ref="A1:BC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,6 +687,11 @@
           <t>anexo_valorUnitarioAnexo</t>
         </is>
       </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>data_hora_extracao</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -718,7 +723,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6064202200013917</t>
+          <t>6064.2022/0001391-7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -919,6 +924,11 @@
           <t>44103582.69</t>
         </is>
       </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>05/05/2026 16:35:43</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -950,7 +960,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>6076202500006776</t>
+          <t>6076.2025/0000677-6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1151,6 +1161,11 @@
           <t>4300000.0</t>
         </is>
       </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>05/05/2026 16:35:43</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1182,7 +1197,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6073202500006001</t>
+          <t>6073.2025/0000600-1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1383,6 +1398,11 @@
           <t>954824.25</t>
         </is>
       </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>05/05/2026 16:35:43</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1414,7 +1434,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6064202200013917</t>
+          <t>6064.2022/0001391-7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1615,6 +1635,11 @@
           <t>3500000.0</t>
         </is>
       </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>05/05/2026 16:35:43</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1646,7 +1671,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6076202500006776</t>
+          <t>6076.2025/0000677-6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1847,6 +1872,11 @@
           <t>15000000.0</t>
         </is>
       </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>05/05/2026 16:35:43</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1878,7 +1908,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>6064202200013917</t>
+          <t>6064.2022/0001391-7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2079,6 +2109,11 @@
           <t>31815317.31</t>
         </is>
       </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>05/05/2026 16:35:43</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2110,7 +2145,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6064202200013917</t>
+          <t>6064.2022/0001391-7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2269,7 +2304,7 @@
         <v>4494470</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>2247234.98</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -2311,6 +2346,11 @@
           <t>4494470.0</t>
         </is>
       </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>05/05/2026 16:35:43</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/base_execucao/empenhos.xlsx
+++ b/base_execucao/empenhos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC8"/>
+  <dimension ref="A1:BD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,6 +688,11 @@
         </is>
       </c>
       <c r="BC1" t="inlineStr">
+        <is>
+          <t>sigla_orgao</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
         <is>
           <t>data_hora_extracao</t>
         </is>
@@ -926,7 +931,12 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>05/05/2026 16:35:43</t>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:19:02</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1173,12 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>05/05/2026 16:35:43</t>
+          <t>SMTUR</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:19:02</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1415,12 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>05/05/2026 16:35:43</t>
+          <t>SMRI</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:19:02</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1657,12 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>05/05/2026 16:35:43</t>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:19:02</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1899,12 @@
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>05/05/2026 16:35:43</t>
+          <t>SMTUR</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:19:02</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2141,12 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>05/05/2026 16:35:43</t>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:19:02</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2383,12 @@
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>05/05/2026 16:35:43</t>
+          <t>SMDET - VAI TEC</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>06/05/2026 15:19:02</t>
         </is>
       </c>
     </row>

--- a/base_execucao/empenhos.xlsx
+++ b/base_execucao/empenhos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD8"/>
+  <dimension ref="A1:BD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,12 +931,12 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>SMDET - VAI TEC</t>
+          <t>SMDET - ADE SAMPA</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>06/05/2026 15:19:02</t>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>06/05/2026 15:19:02</t>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>06/05/2026 15:19:02</t>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>
@@ -1657,12 +1657,12 @@
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>SMDET - VAI TEC</t>
+          <t>SMDET - ADE SAMPA</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>06/05/2026 15:19:02</t>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
         <v>15000000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4000000</v>
+        <v>8000000</v>
       </c>
       <c r="AQ6" t="n">
         <v>4000000</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>06/05/2026 15:19:02</t>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
         <v>31815317.31</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>19309998.54</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>SMDET - VAI TEC</t>
+          <t>SMDET - ADE SAMPA</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>06/05/2026 15:19:02</t>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,249 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>06/05/2026 15:19:02</t>
+          <t>11/05/2026 09:16:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PREFEITURA DO MUNICÍPIO DE SÃO PAULO</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>25286</v>
+      </c>
+      <c r="D9" t="n">
+        <v>51281</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>06/05/2026 00:00:00</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6064.2022/0001391-7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>21154061000183</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>AGENCIA SAO PAULO DE DESENVOLVIMENTO  ADE SAMPA</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>30260</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Secretaria Municipal de Desenvolvimento Econômico e Trabalho</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gabinete do Secretário</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Trabalho</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Fomento ao Trabalho</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Crescimento Econômico e Empregabilidade</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Manutenção e Operação da Agência São Paulo de Desenvolvimento - ADESAM</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Despesas Correntes</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Outras Despesas Correntes</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Transferências a Instituições Privadas sem Fins Lucrativos</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Transferências por meio de Contrato de Gestão - Serviços de Assistênci</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Recursos não vinculados de Impostos</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>Contratos de Gestão</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>Contrato de Gestão</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>001/2022/SMDET</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>30.10.11.334.4012.4440.33508500.00.1.500.9001</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>un</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>Contrato de Gestão 01/2022/SMDET - TA nº 13 - parcela maio</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2500000.0</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>SMDET - ADE SAMPA</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>11/05/2026 09:16:04</t>
         </is>
       </c>
     </row>

--- a/base_execucao/empenhos.xlsx
+++ b/base_execucao/empenhos.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>11/05/2026 09:16:04</t>
+          <t>11/05/2026 14:04:35</t>
         </is>
       </c>
     </row>

--- a/base_execucao/empenhos.xlsx
+++ b/base_execucao/empenhos.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
         <v>8000000</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4000000</v>
+        <v>8000000</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
         <v>2247234.98</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>2247234.98</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>11/05/2026 14:04:35</t>
+          <t>14/05/2026 11:36:24</t>
         </is>
       </c>
     </row>

--- a/base_execucao/empenhos.xlsx
+++ b/base_execucao/empenhos.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
         <v>19309998.54</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>19309998.54</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
         <v>2500000</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>14/05/2026 11:36:24</t>
+          <t>22/05/2026 16:16:42</t>
         </is>
       </c>
     </row>

--- a/base_execucao/empenhos.xlsx
+++ b/base_execucao/empenhos.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
@@ -1855,10 +1855,10 @@
         <v>15000000</v>
       </c>
       <c r="AP6" t="n">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8000000</v>
+        <v>12000000</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>22/05/2026 16:16:42</t>
+          <t>10/06/2026 14:17:35</t>
         </is>
       </c>
     </row>
